--- a/out/Village_map_of_Tiruvallur_Gummidipoondi_Venkuzhi_13.338507_80.040221.xlsx
+++ b/out/Village_map_of_Tiruvallur_Gummidipoondi_Venkuzhi_13.338507_80.040221.xlsx
@@ -638,11 +638,6 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>1, 2, 3A, 3B</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -650,11 +645,6 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>1A, 1B, 2A, 2B, 2C, 2D, 3A, 3B, 4A, 4B, 4C, 5A1, 5A2, 5B, 6, 7</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -662,11 +652,6 @@
           <t>27</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -674,11 +659,6 @@
           <t>28</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4, 5A, 5B</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -686,11 +666,6 @@
           <t>29</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>1, 2</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -698,11 +673,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>1, 2A, 2B, 2C1, 2C2, 3, 4</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -710,11 +680,6 @@
           <t>30</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4A, 4B1, 4B2, 5</t>
-        </is>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -722,11 +687,6 @@
           <t>31</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -734,11 +694,6 @@
           <t>32</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>1, 2</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -746,11 +701,6 @@
           <t>33</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>1A, 1B, 1C, 1D, 1E, 2A, 2B, 3A, 3B</t>
-        </is>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -758,11 +708,6 @@
           <t>34</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>1, 2</t>
-        </is>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -770,11 +715,6 @@
           <t>35</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>1, 2A, 2B1A, 2B1B, 2B2, 2B3, 3, 4, 5, 6</t>
-        </is>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -782,11 +722,6 @@
           <t>36</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>1A, 1B1A, 1B1B, 1B2, 1B3, 2A, 2B1A, 2B1B, 2B2, 2B3, 2C, 2D</t>
-        </is>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -794,11 +729,6 @@
           <t>37</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>1, 2A, 2B, 3, 4, 5</t>
-        </is>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -806,11 +736,6 @@
           <t>38</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>1, 2A, 2B, 3, 4, 5A, 5B, 5C, 5D, 6, 7</t>
-        </is>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -818,11 +743,6 @@
           <t>39</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>1A, 1B, 1C, 1D, 1E, 1F, 1G1, 1G2, 2A, 2B, 2C1, 2C2, 2C3, 2D, 2E</t>
-        </is>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -830,11 +750,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>1, 2, 3</t>
-        </is>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -842,11 +757,6 @@
           <t>40</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4, 5, 6, 7A, 7B, 7C, 8, 9A, 9B</t>
-        </is>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -854,11 +764,6 @@
           <t>41</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>1, 2, 3A, 3B, 4, 5</t>
-        </is>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -866,11 +771,6 @@
           <t>42</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4A, 4B, 5, 6</t>
-        </is>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -878,11 +778,6 @@
           <t>43</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>1, 2</t>
-        </is>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -890,11 +785,6 @@
           <t>44</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>1, 2A, 2B, 3, 4A, 4B, 5A, 5B, 6, 7, 8</t>
-        </is>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -902,11 +792,6 @@
           <t>45</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -914,11 +799,6 @@
           <t>46</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -926,11 +806,6 @@
           <t>47</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -938,11 +813,6 @@
           <t>48</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>1, 2</t>
-        </is>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -950,11 +820,6 @@
           <t>49</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -962,11 +827,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -974,11 +834,6 @@
           <t>50</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>1A, 1B, 1C, 1D, 1E, 1F, 1G, 2A, 2B, 2C, 2D, 2E, 2F, 2G, 3A, 3B, 3C, 3D, 3E, 3F, 3G, 3H, 3I, 3J, 4A, 4B, 4C, 5A1, 5A2, 5B, 5C, 5D, 5E, 5F, 6A, 6B</t>
-        </is>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -986,11 +841,6 @@
           <t>51</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -998,11 +848,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1010,11 +855,6 @@
           <t>7</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1022,21 +862,11 @@
           <t>8</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>1A1, 1A2, 1B1, 1B2, 1C1, 1C2, 1D, 2</t>
         </is>
       </c>
     </row>

--- a/out/Village_map_of_Tiruvallur_Gummidipoondi_Venkuzhi_13.338507_80.040221.xlsx
+++ b/out/Village_map_of_Tiruvallur_Gummidipoondi_Venkuzhi_13.338507_80.040221.xlsx
@@ -638,6 +638,11 @@
           <t>25</t>
         </is>
       </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>1, 2, 3A, 3B</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -645,6 +650,11 @@
           <t>26</t>
         </is>
       </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2A, 2B, 2C, 2D, 3A, 3B, 4A, 4B, 4C, 5A1, 5A2, 5B, 6, 7</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -652,6 +662,11 @@
           <t>27</t>
         </is>
       </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -659,6 +674,11 @@
           <t>28</t>
         </is>
       </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5A, 5B</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -666,6 +686,11 @@
           <t>29</t>
         </is>
       </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -673,6 +698,11 @@
           <t>3</t>
         </is>
       </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 2C1, 2C2, 3, 4</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -680,6 +710,11 @@
           <t>30</t>
         </is>
       </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4A, 4B1, 4B2, 5</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -687,6 +722,11 @@
           <t>31</t>
         </is>
       </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -694,6 +734,11 @@
           <t>32</t>
         </is>
       </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -701,6 +746,11 @@
           <t>33</t>
         </is>
       </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 1D, 1E, 2A, 2B, 3A, 3B</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -708,11 +758,21 @@
           <t>34</t>
         </is>
       </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
           <t>35</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B1A, 2B1B, 2B2, 2B3, 3, 4, 5, 6</t>
         </is>
       </c>
     </row>

--- a/out/Village_map_of_Tiruvallur_Gummidipoondi_Venkuzhi_13.338507_80.040221.xlsx
+++ b/out/Village_map_of_Tiruvallur_Gummidipoondi_Venkuzhi_13.338507_80.040221.xlsx
@@ -974,6 +974,11 @@
           <t>50</t>
         </is>
       </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 1D, 1E, 1F, 1G, 2A, 2B, 2C, 2D, 2E, 2F, 2G, 3A, 3B, 3C, 3D, 3E, 3F, 3G, 3H, 3I, 3J, 4A, 4B, 4C, 5A1, 5A2, 5B, 5C, 5D, 5E, 5F, 6A, 6B</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -981,6 +986,11 @@
           <t>51</t>
         </is>
       </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -988,6 +998,11 @@
           <t>6</t>
         </is>
       </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -995,6 +1010,11 @@
           <t>7</t>
         </is>
       </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1002,11 +1022,21 @@
           <t>8</t>
         </is>
       </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
           <t>9</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1B1, 1B2, 1C1, 1C2, 1D, 2</t>
         </is>
       </c>
     </row>

--- a/out/Village_map_of_Tiruvallur_Gummidipoondi_Venkuzhi_13.338507_80.040221.xlsx
+++ b/out/Village_map_of_Tiruvallur_Gummidipoondi_Venkuzhi_13.338507_80.040221.xlsx
@@ -782,6 +782,11 @@
           <t>36</t>
         </is>
       </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>1A, 1B1A, 1B1B, 1B2, 1B3, 2A, 2B1A, 2B1B, 2B2, 2B3, 2C, 2D</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -789,6 +794,11 @@
           <t>37</t>
         </is>
       </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 3, 4, 5</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -796,6 +806,11 @@
           <t>38</t>
         </is>
       </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 3, 4, 5A, 5B, 5C, 5D, 6, 7</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -803,6 +818,11 @@
           <t>39</t>
         </is>
       </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 1D, 1E, 1F, 1G1, 1G2, 2A, 2B, 2C1, 2C2, 2C3, 2D, 2E</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -810,11 +830,21 @@
           <t>4</t>
         </is>
       </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
           <t>40</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6, 7A, 7B, 7C, 8, 9A, 9B</t>
         </is>
       </c>
     </row>

--- a/out/Village_map_of_Tiruvallur_Gummidipoondi_Venkuzhi_13.338507_80.040221.xlsx
+++ b/out/Village_map_of_Tiruvallur_Gummidipoondi_Venkuzhi_13.338507_80.040221.xlsx
@@ -854,6 +854,11 @@
           <t>41</t>
         </is>
       </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>1, 2, 3A, 3B, 4, 5</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -861,6 +866,11 @@
           <t>42</t>
         </is>
       </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4A, 4B, 5, 6</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -868,6 +878,11 @@
           <t>43</t>
         </is>
       </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -875,6 +890,11 @@
           <t>44</t>
         </is>
       </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 3, 4A, 4B, 5A, 5B, 6, 7, 8</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -882,6 +902,11 @@
           <t>45</t>
         </is>
       </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -889,6 +914,11 @@
           <t>46</t>
         </is>
       </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -896,6 +926,11 @@
           <t>47</t>
         </is>
       </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -903,6 +938,11 @@
           <t>48</t>
         </is>
       </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -910,6 +950,11 @@
           <t>49</t>
         </is>
       </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -917,6 +962,11 @@
           <t>5</t>
         </is>
       </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -924,6 +974,11 @@
           <t>50</t>
         </is>
       </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 1D, 1E, 1F, 1G, 2A, 2B, 2C, 2D, 2E, 2F, 2G, 3A, 3B, 3C, 3D, 3E, 3F, 3G, 3H, 3I, 3J, 4A, 4B, 4C, 5A1, 5A2, 5B, 5C, 5D, 5E, 5F, 6A, 6B</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -931,6 +986,11 @@
           <t>51</t>
         </is>
       </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -938,6 +998,11 @@
           <t>6</t>
         </is>
       </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -945,6 +1010,11 @@
           <t>7</t>
         </is>
       </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -952,11 +1022,21 @@
           <t>8</t>
         </is>
       </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
           <t>9</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1B1, 1B2, 1C1, 1C2, 1D, 2</t>
         </is>
       </c>
     </row>
